--- a/expedientes_pjn_detalle.xlsx
+++ b/expedientes_pjn_detalle.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F178"/>
+  <dimension ref="A1:G179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,11 @@
           <t>Último movimiento</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -479,6 +484,7 @@
           <t>26/06/2014: PASE - JUZGADO FEDERAL DE SANTA FE 2</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -511,6 +517,7 @@
           <t>31/03/1992: PASE - CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBLICOS</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -543,6 +550,7 @@
           <t>7/04/2003: PASE - JUZGADO FEDERAL DE SANTA FE 2</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -575,6 +583,7 @@
           <t>Oficina: CIV: Fecha: 4/08/2025 - Tipo actuacion: EXPEDIENTE DESPARALIZADO</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -607,6 +616,7 @@
           <t>14/05/2018: CAMBIO DE ESTADO DE EXPEDIENTE - EN LETRA</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -639,6 +649,7 @@
           <t>2/06/2014: EVENTO - PROV.SIMPLE DEFINITIVA -</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -671,6 +682,7 @@
           <t>31/03/2004: PASE - JUZGADO FEDERAL DE SANTA FE 2</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -703,6 +715,7 @@
           <t>29/08/2017: CAMBIO DE ESTADO DE EXPEDIENTE - EN LETRA</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -735,6 +748,7 @@
           <t>26/05/2014: EVENTO - PROV.SIMPLE DEFINITIVA -</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -767,6 +781,7 @@
           <t>11/10/1994: PASE - ADMINISTRACION NACIONAL DE SEGURIDAD SOCIAL (A.N.Se.S.)</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -799,6 +814,7 @@
           <t>Oficina: CIV: Fecha: 30/05/2023 - Tipo actuacion: ESCRITO INCORPORADO</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -831,6 +847,7 @@
           <t>3/06/1994: PASE - CORTE SUPREMA DE JUSTICIA DE LA NACIÓN</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -863,6 +880,7 @@
           <t>1/03/2018: CEDULA ELECTRONICA PARTE - CEDULA N° 18000015265430 - NOTIFICADO EL 01/03/2018 16:13</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -895,6 +913,7 @@
           <t>2/10/2018: CAMBIO DE ESTADO DE EXPEDIENTE - CONFRONTE OFICIO</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -927,6 +946,7 @@
           <t>2/10/2017: CEDULA INCORPORADA - Notificación Notificada 29/09/2017 - Positivo 55 / 55</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -959,6 +979,7 @@
           <t>29/09/1992: PASE - COMISION NACIONAL DE PREVISION SOCIAL</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -991,6 +1012,7 @@
           <t>14/05/2018: CAMBIO DE ESTADO DE EXPEDIENTE - PARA RETIRAR OFICIO</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1023,6 +1045,7 @@
           <t>23/08/2017: CAMBIO DE ESTADO DE EXPEDIENTE - EN LETRA</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1055,6 +1078,7 @@
           <t>22/05/2014: EVENTO - PROV.SIMPLE DEFINITIVA -</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1087,6 +1111,7 @@
           <t>10/03/2009: PASE - CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1119,6 +1144,7 @@
           <t>Oficina: CIV: Fecha: 24/06/2019 - Tipo actuacion: CAMBIO DE ESTADO DE EXPEDIENTE</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1151,6 +1177,7 @@
           <t>26/08/2014: PASE - JUZGADO FEDERAL DE SANTA FE 2</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1183,6 +1210,7 @@
           <t>Oficina: CIV: Fecha: 4/04/2023 - Tipo actuacion: MOVIMIENTO</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1215,6 +1243,7 @@
           <t>3/07/2001: PASE - JUZGADO FEDERAL DE SANTA FE 2</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1247,6 +1276,7 @@
           <t>26/07/2017: CAMBIO DE ESTADO DE EXPEDIENTE - PARA RETIRAR OFICIO</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1279,6 +1309,7 @@
           <t>7/08/1995: PASE - ADMINISTRACION NACIONAL DE SEGURIDAD SOCIAL (A.N.Se.S.)</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1311,6 +1342,7 @@
           <t>Oficina: CIV: Fecha: 24/06/2019 - Tipo actuacion: CAMBIO DE ESTADO DE EXPEDIENTE</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1343,6 +1375,7 @@
           <t>20/09/1995: PASE - ADMINISTRACION NACIONAL DE SEGURIDAD SOCIAL (A.N.Se.S.)</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1375,6 +1408,7 @@
           <t>Oficina: CIV: Fecha: 12/02/2026 - Tipo actuacion: DEO</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1407,6 +1441,7 @@
           <t>20/04/2018: CAMBIO DE ESTADO DE EXPEDIENTE - PARA RETIRAR OFICIO</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1439,6 +1474,7 @@
           <t>4/09/2017: CAMBIO DE ESTADO DE EXPEDIENTE - PARA RETIRAR OFICIO</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1471,6 +1507,7 @@
           <t>Oficina: CIV: Fecha: 13/05/2025 - Tipo actuacion: FIRMA DESPACHO</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1503,6 +1540,7 @@
           <t>16/06/2017: CAMBIO DE ESTADO DE EXPEDIENTE - EN LETRA</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1535,6 +1573,7 @@
           <t>Oficina: CIV: Fecha: 25/10/2023 - Tipo actuacion: MOVIMIENTO</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1567,6 +1606,7 @@
           <t>28/08/2006: PASE - CORTE SUPREMA DE JUSTICIA DE LA NACIÓN - ARCHIVO GENERAL</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1599,6 +1639,7 @@
           <t>11/10/1994: PASE - ADMINISTRACION NACIONAL DE SEGURIDAD SOCIAL (A.N.Se.S.)</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1631,6 +1672,7 @@
           <t>25/04/2016: FIRMA DESPACHO - AGREGUESE OFICIO CON CARGO DE LA ANSES 62 / 62</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1663,6 +1705,7 @@
           <t>23/05/2014: EVENTO - PROV.SIMPLE DEFINITIVA -</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1695,6 +1738,7 @@
           <t>23/05/2017: CAMBIO DE ESTADO DE EXPEDIENTE - PARA RETIRAR OFICIO</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1727,6 +1771,7 @@
           <t>11/04/2018: CAMBIO DE ESTADO DE EXPEDIENTE - PARA RETIRAR OFICIO</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1759,6 +1804,7 @@
           <t>19/05/2014: EVENTO - PROV.SIMPLE DEFINITIVA -</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1791,6 +1837,7 @@
           <t>28/06/2007: PASE - CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1823,6 +1870,7 @@
           <t>Oficina: CIV: Fecha: 17/12/2025 - Tipo actuacion: MOVIMIENTO</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1855,6 +1903,7 @@
           <t>10/11/1992: PASE - INSTITUTO NACIONAL DE PREVISION SOCIAL</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1887,6 +1936,7 @@
           <t>27/04/2017: FIRMA DESPACHO - AGREGUESE 66 / 66</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1919,6 +1969,7 @@
           <t>9/05/1994: PASE - CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBLICOS</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1951,6 +2002,7 @@
           <t>1/03/2018: CAMBIO DE ESTADO DE EXPEDIENTE - EN LETRA</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1983,6 +2035,7 @@
           <t>21/08/2014: EVENTO - PROV.SIMPLE DEFINITIVA - REMITIDO AL INTERIOR (MGE)</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2015,6 +2068,7 @@
           <t>Oficina: CIV: Fecha: 20/05/2025 - Tipo actuacion: CEDULA ELECTRONICA TRIBUNAL</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2047,6 +2101,7 @@
           <t>Oficina: FIS: Fecha: 9/06/2026 - Tipo actuacion: MOVIMIENTO</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2079,6 +2134,7 @@
           <t>21/08/2014: EVENTO - PROV.SIMPLE DEFINITIVA - REMITIDO AL INTERIOR (MGE)</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2111,6 +2167,7 @@
           <t>18/04/2016: FIRMA DESPACHO - AGREGUESE OFICIO CON CARGO DE LA ANSES 78 / 78</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2143,6 +2200,7 @@
           <t>12/09/1996: PASE - CORTE SUPREMA DE JUSTICIA DE LA NACIÓN</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2175,6 +2233,7 @@
           <t>20/02/2018: CAMBIO DE ESTADO DE EXPEDIENTE - EN LETRA</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2207,6 +2266,7 @@
           <t>22/08/2014: EVENTO - PROV.SIMPLE DEFINITIVA - REMITIDO AL INTERIOR (MGE)</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2239,6 +2299,7 @@
           <t>Oficina: LEY: Fecha: 12/02/2026 - Tipo actuacion: DEO</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2271,6 +2332,7 @@
           <t>27/09/2016: MOVIMIENTO - EN LETRA</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2303,6 +2365,7 @@
           <t>28/04/2014: PASE - CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2335,6 +2398,7 @@
           <t>4/06/1992: PASE - CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBLICOS</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2367,6 +2431,7 @@
           <t>18/10/2018: CAMBIO DE ESTADO DE EXPEDIENTE - EN LETRA</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2399,6 +2464,7 @@
           <t>6/06/1995: PASE - ADMINISTRACION NACIONAL DE SEGURIDAD SOCIAL (A.N.Se.S.)</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2431,6 +2497,7 @@
           <t>13/08/2001: PASE - CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2463,6 +2530,7 @@
           <t>24/05/2018: CAMBIO DE ESTADO DE EXPEDIENTE - EN LETRA</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2495,6 +2563,7 @@
           <t>17/09/2002: PASE - CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2527,6 +2596,7 @@
           <t>27/04/2011: PASE - CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2559,6 +2629,7 @@
           <t>7/02/2006: PASE - CORTE SUPREMA DE JUSTICIA DE LA NACIÓN - ARCHIVO GENERAL</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2591,6 +2662,7 @@
           <t>14/02/1994: PASE - CORTE SUPREMA DE JUSTICIA DE LA NACIÓN</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2623,6 +2695,7 @@
           <t>Oficina: LEY: Fecha: 10/02/2025 - Tipo actuacion: MOVIMIENTO</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2655,6 +2728,7 @@
           <t>10/06/2014: EVENTO - PROV.SIMPLE DEFINITIVA -</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2687,6 +2761,7 @@
           <t>8/09/2017: CAMBIO DE ESTADO DE EXPEDIENTE - EN LETRA</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2719,6 +2794,7 @@
           <t>7/12/2010: PASE - JUZGADO FEDERAL DE SANTA FE 2</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2751,6 +2827,7 @@
           <t>Oficina: CIV: Fecha: 9/06/2026 - Tipo actuacion: CEDULA ELECTRONICA PARTE</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2783,6 +2860,7 @@
           <t>Oficina: CIV: Fecha: 3/06/2025 - Tipo actuacion: DEO</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2815,6 +2893,7 @@
           <t>Oficina: CIV: Fecha: 16/03/2021 - Tipo actuacion: CEDULA ELECTRONICA PARTE</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2847,6 +2926,7 @@
           <t>Oficina: LEY: Fecha: 8/11/2023 - Tipo actuacion: FIRMA DESPACHO</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2879,6 +2959,7 @@
           <t>18/06/1993: PASE - INSTITUTO NACIONAL DE PREVISION SOCIAL</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2911,6 +2992,7 @@
           <t>3/03/2017: CAMBIO DE ESTADO DE EXPEDIENTE - EN LETRA</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2943,6 +3025,7 @@
           <t>Oficina: FIS: Fecha: 27/05/2025 - Tipo actuacion: DEO</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2975,6 +3058,7 @@
           <t>7/09/2018: CAMBIO DE ESTADO DE EXPEDIENTE - EN LETRA</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3007,6 +3091,7 @@
           <t>Oficina: CIV: Fecha: 22/09/2022 - Tipo actuacion: MOVIMIENTO</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3039,6 +3124,7 @@
           <t>Oficina: CIV: Fecha: 16/04/2024 - Tipo actuacion: MOVIMIENTO</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3071,6 +3157,7 @@
           <t>20/05/2014: EVENTO - PROV.SIMPLE DEFINITIVA -</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3103,6 +3190,7 @@
           <t>4/03/2010: PASE - CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3135,6 +3223,7 @@
           <t>6/07/1995: PASE - ADMINISTRACION NACIONAL DE SEGURIDAD SOCIAL (A.N.Se.S.)</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3167,6 +3256,7 @@
           <t>13/05/2011: PASE - JUZGADO FEDERAL DE SANTA FE 2</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3199,6 +3289,7 @@
           <t>14/02/1994: PASE - CORTE SUPREMA DE JUSTICIA DE LA NACIÓN</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3231,6 +3322,7 @@
           <t>Oficina: LEY: Fecha: 2/12/2025 - Tipo actuacion: MOVIMIENTO</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3263,6 +3355,7 @@
           <t>2/02/2018: CAMBIO DE ESTADO DE EXPEDIENTE - PARA RETIRAR OFICIO</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3295,6 +3388,7 @@
           <t>27/04/2012: PASE - JUZGADO FEDERAL DE SANTA FE 2</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3327,6 +3421,7 @@
           <t>Oficina: MEC: Fecha: 24/06/2026 - Tipo actuacion: RECEPCION PASE</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3359,6 +3454,7 @@
           <t>17/10/1994: PASE - ADMINISTRACION NACIONAL DE SEGURIDAD SOCIAL (A.N.Se.S.)</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3391,6 +3487,7 @@
           <t>21/10/2016: MOVIMIENTO - EN LETRA</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3423,6 +3520,7 @@
           <t>Oficina: CIV: Fecha: 25/06/2021 - Tipo actuacion: MOVIMIENTO</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3455,6 +3553,7 @@
           <t>Oficina: LEY: Fecha: 26/06/2019 - Tipo actuacion: CAMBIO DE ESTADO DE EXPEDIENTE</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3487,6 +3586,7 @@
           <t>Oficina: CIV: Fecha: 20/02/2020 - Tipo actuacion: CAMBIO DE ESTADO DE EXPEDIENTE</t>
         </is>
       </c>
+      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3519,6 +3619,7 @@
           <t>7/12/2001: PASE - CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3551,6 +3652,7 @@
           <t>Oficina: LEY: Fecha: 4/03/2026 - Tipo actuacion: MOVIMIENTO</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3583,6 +3685,7 @@
           <t>6/10/2016: MOVIMIENTO - EN LETRA</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3615,6 +3718,7 @@
           <t>Oficina: CIV: Fecha: 22/08/2024 - Tipo actuacion: MOVIMIENTO</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3647,6 +3751,7 @@
           <t>9/03/2007: PASE - CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3679,6 +3784,7 @@
           <t>3/04/2014: PASE - CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3711,6 +3817,7 @@
           <t>14/08/2017: CAMBIO DE ESTADO DE EXPEDIENTE - EN LETRA</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3743,6 +3850,7 @@
           <t>29/09/2016: MOVIMIENTO - EN LETRA</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3775,6 +3883,7 @@
           <t>19/06/2018: CAMBIO DE ESTADO DE EXPEDIENTE - PARA RETIRAR OFICIO</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3807,6 +3916,7 @@
           <t>28/09/2017: CAMBIO DE ESTADO DE EXPEDIENTE - EN LETRA</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3839,6 +3949,7 @@
           <t>Oficina: LEY: Fecha: 13/05/2026 - Tipo actuacion: MOVIMIENTO</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3871,6 +3982,7 @@
           <t>23/05/2014: EVENTO - PROV.SIMPLE DEFINITIVA -</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3903,6 +4015,7 @@
           <t>24/09/2014: PASE - JUZGADO FEDERAL DE SANTA FE 2</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3935,6 +4048,7 @@
           <t>18/04/2018: CAMBIO DE ESTADO DE EXPEDIENTE - EN LETRA</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3967,6 +4081,7 @@
           <t>3/11/2010: PASE - CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3999,6 +4114,7 @@
           <t>6/11/2001: PASE - CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4031,6 +4147,7 @@
           <t>Oficina: LEY: Fecha: 19/11/2020 - Tipo actuacion: MOVIMIENTO</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4063,6 +4180,7 @@
           <t>10/09/1992: PASE - CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBLICOS</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4095,6 +4213,7 @@
           <t>11/09/2014: EVENTO - PROV.SIMPLE DEFINITIVA - REMITIDO AL INTERIOR (MGE)</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4127,6 +4246,7 @@
           <t>Oficina: FIS: Fecha: 10/04/2024 - Tipo actuacion: RECEPCION PASE</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4159,6 +4279,7 @@
           <t>31/08/2015: FIRMA DESPACHO - AGREGUESE OFICIO DE REMISIÓN DE ADM Y COPIAS CERTIFICADAS 61 / 61</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4191,6 +4312,7 @@
           <t>Oficina: CIV: Fecha: 24/05/2022 - Tipo actuacion: MOVIMIENTO</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4223,6 +4345,7 @@
           <t>25/11/2014: PASE - JUZGADO FEDERAL DE SANTA FE 2</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4255,6 +4378,7 @@
           <t>Oficina: CIV: Fecha: 4/06/2026 - Tipo actuacion: MOVIMIENTO</t>
         </is>
       </c>
+      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4287,6 +4411,7 @@
           <t>Oficina: CIV: Fecha: 4/10/2019 - Tipo actuacion: CAMBIO DE ESTADO DE EXPEDIENTE</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4319,6 +4444,7 @@
           <t>8/04/2016: FIRMA DESPACHO - AGREGUESE OFICIO CON CARGO DE LA ANSES 71 / 71</t>
         </is>
       </c>
+      <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4351,6 +4477,7 @@
           <t>Oficina: CIV: Fecha: 19/09/2019 - Tipo actuacion: CAMBIO DE ESTADO DE EXPEDIENTE</t>
         </is>
       </c>
+      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4383,6 +4510,7 @@
           <t>20/05/1994: PASE - CAJA NAC DE PREV DE LA INDUSTRIA, COM Y ACT CIVILES</t>
         </is>
       </c>
+      <c r="G124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4415,6 +4543,7 @@
           <t>13/02/2017: CAMBIO DE ESTADO DE EXPEDIENTE - EN LETRA</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4447,6 +4576,7 @@
           <t>22/08/2014: EVENTO - PROV.SIMPLE DEFINITIVA - REMITIDO AL INTERIOR (MGE)</t>
         </is>
       </c>
+      <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4479,6 +4609,7 @@
           <t>Oficina: CIV: Fecha: 22/06/2022 - Tipo actuacion: MOVIMIENTO</t>
         </is>
       </c>
+      <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4511,6 +4642,7 @@
           <t>15/10/1992: PASE - CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBLICOS</t>
         </is>
       </c>
+      <c r="G128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4543,6 +4675,7 @@
           <t>Oficina: FIS: Fecha: 21/11/2019 - Tipo actuacion: CAMBIO DE ESTADO DE EXPEDIENTE</t>
         </is>
       </c>
+      <c r="G129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4575,6 +4708,7 @@
           <t>27/05/2014: EVENTO - PROV.SIMPLE DEFINITIVA -</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4607,6 +4741,7 @@
           <t>Oficina: LEY: Fecha: 5/11/2024 - Tipo actuacion: MOVIMIENTO</t>
         </is>
       </c>
+      <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4639,6 +4774,7 @@
           <t>10/02/2006: INFORMACION - COMENTARIO: PRIMERA CERT.SENT.DEF.CUMPLIDA</t>
         </is>
       </c>
+      <c r="G132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4671,6 +4807,7 @@
           <t>18/10/2016: MOVIMIENTO - EN LETRA</t>
         </is>
       </c>
+      <c r="G133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4703,6 +4840,7 @@
           <t>10/12/2001: PASE - ADMINISTRACION NACIONAL DE SEGURIDAD SOCIAL (A.N.Se.S.)</t>
         </is>
       </c>
+      <c r="G134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4735,6 +4873,7 @@
           <t>20/05/2014: EVENTO - PROV.SIMPLE DEFINITIVA -</t>
         </is>
       </c>
+      <c r="G135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4767,6 +4906,7 @@
           <t>4/06/2004: PASE - CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
         </is>
       </c>
+      <c r="G136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4799,6 +4939,7 @@
           <t>Oficina: LEY: Fecha: 7/08/2025 - Tipo actuacion: FIRMA DESPACHO</t>
         </is>
       </c>
+      <c r="G137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4831,6 +4972,7 @@
           <t>Oficina: LEY: Fecha: 29/11/2021 - Tipo actuacion: MOVIMIENTO</t>
         </is>
       </c>
+      <c r="G138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4863,6 +5005,7 @@
           <t>15/08/2014: EVENTO - PROV.SIMPLE DEFINITIVA - REMITIDO AL INTERIOR (MGE)</t>
         </is>
       </c>
+      <c r="G139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4895,6 +5038,7 @@
           <t>25/10/2018: CAMBIO DE ESTADO DE EXPEDIENTE - PARA RETIRAR OFICIO</t>
         </is>
       </c>
+      <c r="G140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4927,6 +5071,7 @@
           <t>13/08/2014: EVENTO - PROV.SIMPLE DEFINITIVA - REMITIDO AL INTERIOR (MGE)</t>
         </is>
       </c>
+      <c r="G141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4959,6 +5104,7 @@
           <t>5/10/2017: CAMBIO DE ESTADO DE EXPEDIENTE - PARA RETIRAR OFICIO</t>
         </is>
       </c>
+      <c r="G142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4991,6 +5137,7 @@
           <t>8/09/2014: EVENTO - PROV.SIMPLE DEFINITIVA - REMITIDO AL INTERIOR (MGE)</t>
         </is>
       </c>
+      <c r="G143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5023,6 +5170,7 @@
           <t>Oficina: LEY: Fecha: 26/09/2024 - Tipo actuacion: DEO</t>
         </is>
       </c>
+      <c r="G144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5055,6 +5203,7 @@
           <t>17/10/2017: CAMBIO DE ESTADO DE EXPEDIENTE - EN LETRA</t>
         </is>
       </c>
+      <c r="G145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5087,6 +5236,7 @@
           <t>25/08/2014: EVENTO - PROV.SIMPLE DEFINITIVA - REMITIDO AL INTERIOR (MGE)</t>
         </is>
       </c>
+      <c r="G146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5119,6 +5269,7 @@
           <t>14/05/2018: CAMBIO DE ESTADO DE EXPEDIENTE - EN LETRA</t>
         </is>
       </c>
+      <c r="G147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5151,6 +5302,7 @@
           <t>15/08/2014: EVENTO - PROV.SIMPLE DEFINITIVA - REMITIDO AL INTERIOR (MGE)</t>
         </is>
       </c>
+      <c r="G148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5183,6 +5335,7 @@
           <t>26/05/2014: EVENTO - PROV.SIMPLE DEFINITIVA -</t>
         </is>
       </c>
+      <c r="G149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5215,6 +5368,7 @@
           <t>22/02/2018: CAMBIO DE ESTADO DE EXPEDIENTE - EN LETRA</t>
         </is>
       </c>
+      <c r="G150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5247,6 +5401,7 @@
           <t>4/03/1994: PASE - CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBLICOS</t>
         </is>
       </c>
+      <c r="G151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5279,6 +5434,7 @@
           <t>14/11/2017: CAMBIO DE ESTADO DE EXPEDIENTE - PARA RETIRAR OFICIO</t>
         </is>
       </c>
+      <c r="G152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5311,6 +5467,7 @@
           <t>Oficina: FIS: Fecha: 10/04/2024 - Tipo actuacion: RECEPCION PASE</t>
         </is>
       </c>
+      <c r="G153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5343,6 +5500,7 @@
           <t>18/11/1993: PASE - DIR NAC. DE RECAUDACION PREVISIONAL</t>
         </is>
       </c>
+      <c r="G154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5375,6 +5533,7 @@
           <t>29/09/2011: PASE - CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
         </is>
       </c>
+      <c r="G155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5407,6 +5566,7 @@
           <t>Oficina: LEY: Fecha: 10/02/2026 - Tipo actuacion: DEO</t>
         </is>
       </c>
+      <c r="G156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5439,6 +5599,7 @@
           <t>Oficina: CIV: Fecha: 2/02/2021 - Tipo actuacion: MOVIMIENTO</t>
         </is>
       </c>
+      <c r="G157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5471,6 +5632,7 @@
           <t>Oficina: CIV: Fecha: 4/03/2026 - Tipo actuacion: EVENTO</t>
         </is>
       </c>
+      <c r="G158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5503,6 +5665,7 @@
           <t>19/11/2010: PASE - JUZGADO FEDERAL DE SANTA FE 2</t>
         </is>
       </c>
+      <c r="G159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5535,6 +5698,7 @@
           <t>13/03/2009: PASE - JUZGADO FEDERAL DE SANTA FE 2</t>
         </is>
       </c>
+      <c r="G160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5567,6 +5731,7 @@
           <t>Oficina: RSA: Fecha: 26/03/2026 - Tipo actuacion: EVENTO</t>
         </is>
       </c>
+      <c r="G161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5599,6 +5764,7 @@
           <t>19/08/2014: EVENTO - PROV.SIMPLE DEFINITIVA - REMITIDO AL INTERIOR (MGE)</t>
         </is>
       </c>
+      <c r="G162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5631,6 +5797,7 @@
           <t>21/08/1992: PASE - CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBLICOS</t>
         </is>
       </c>
+      <c r="G163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5663,6 +5830,7 @@
           <t>27/09/2001: PASE - CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
         </is>
       </c>
+      <c r="G164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5695,6 +5863,7 @@
           <t>3/04/1991: PASE - CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBLICOS</t>
         </is>
       </c>
+      <c r="G165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5727,6 +5896,7 @@
           <t>10/03/1998: INFORMACION - COMENTARIO: OF. A LA C.S.J.N.</t>
         </is>
       </c>
+      <c r="G166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5759,6 +5929,7 @@
           <t>Oficina: CIV: Fecha: 2/02/2026 - Tipo actuacion: DEO</t>
         </is>
       </c>
+      <c r="G167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5791,6 +5962,7 @@
           <t>6/08/1991: PASE - CAJA NAC DE PREV DE LA INDUSTRIA, COM Y ACT CIVILES</t>
         </is>
       </c>
+      <c r="G168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5823,6 +5995,7 @@
           <t>17/10/1994: PASE - ADMINISTRACION NACIONAL DE SEGURIDAD SOCIAL (A.N.Se.S.)</t>
         </is>
       </c>
+      <c r="G169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5855,6 +6028,7 @@
           <t>Oficina: FIS: Fecha: 28/02/2018 - Tipo actuacion: CAMBIO DE ESTADO DE EXPEDIENTE</t>
         </is>
       </c>
+      <c r="G170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5887,6 +6061,7 @@
           <t>26/04/2018: CAMBIO DE ESTADO DE EXPEDIENTE - EN LETRA</t>
         </is>
       </c>
+      <c r="G171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5919,6 +6094,7 @@
           <t>7/06/2017: CAMBIO DE ESTADO DE EXPEDIENTE - EN LETRA</t>
         </is>
       </c>
+      <c r="G172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5951,6 +6127,7 @@
           <t>Oficina: CIV: Fecha: 7/10/2021 - Tipo actuacion: MOVIMIENTO</t>
         </is>
       </c>
+      <c r="G173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5983,6 +6160,7 @@
           <t>8/08/2017: FIRMA DESPACHO - AGREGUESE OFICIO CON CARGO DE LA ANSES 92 / 92</t>
         </is>
       </c>
+      <c r="G174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6015,6 +6193,7 @@
           <t>4/11/1993: PASE - CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBLICOS</t>
         </is>
       </c>
+      <c r="G175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6047,6 +6226,7 @@
           <t>8/11/1993: PASE - SUPERIOR TRIBUNAL DE JUSTICIA DE ROSARIO</t>
         </is>
       </c>
+      <c r="G176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6079,6 +6259,7 @@
           <t>5/10/1994: PASE - CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBLICOS</t>
         </is>
       </c>
+      <c r="G177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6107,6 +6288,40 @@
         </is>
       </c>
       <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>53001022/2006</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 1 - SECRETARIA LEYES ESPECIALES</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>CARDINALI, ZELMA ANTONIA C/ ANSES /S ORDINARIO (REAJUSTE</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>EN LETRA</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>2/02/2016</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>No pude volver a la lista</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/expedientes_pjn_detalle.xlsx
+++ b/expedientes_pjn_detalle.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G179"/>
+  <dimension ref="A1:G267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6323,6 +6323,2906 @@
         </is>
       </c>
     </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>CSS 077991/1994</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE LA SEGURIDAD SOCIAL - SALA 3</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>CAMPANELLA GILBERTO ANGEL C/ ANSES S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>22/06/1995</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>30/08/1995: PASE - ADMINISTRACION NACIONAL DE SEGURIDAD SOCIAL (A.N.Se.S.)</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>FRO 032784/2015</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE RAFAELA - SECRETARIA CIVIL</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>CANAVESE, ROGELIO DOMINGO SIMON C/ ANSES S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>EN LETRA</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>25/11/2025</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Oficina: CIV: Fecha: 25/11/2025 - Tipo actuacion: DEO</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>CSS 025526/1990</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE LA SEGURIDAD SOCIAL - SALA 2</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>CANELO SEGUNDO ATILIO C/ INPS-COMISION NACIONAL DE PREVISION SOCIAL S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>16/09/1991</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>21/11/1991: PASE - COMISION NACIONAL DE PREVISION SOCIAL</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>CSS 029570/1992</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE LA SEGURIDAD SOCIAL - SALA 3</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>CANNATARO DE MASCHERONI ADALGISA C/ INPS-CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBL. S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>3/11/1999</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>27/08/2001: PASE - ADMINISTRACION NACIONAL DE SEGURIDAD SOCIAL (A.N.Se.S.)</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>CSS 019024/2010</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE LA SEGURIDAD SOCIAL - SALA 3</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>CAPPELLETTI OSCAR DOMINGO C/ ANSES S/RETIRO POR INVALIDEZ (ART 49 P.4 LEY 24241)</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>7/06/2012</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>21/09/2012: PASE - COMISION MEDICA CENTRAL</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>FRO 012366/2014</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 1 - SECRETARIA EJECUCION FISCAL</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>CARABALLO, MERCEDES C/ ANSES S/EJECUCIÓN PREVISIONAL</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>CONFRONTE</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>24/05/2017</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>24/05/2017: CAMBIO DE ESTADO DE EXPEDIENTE - CONFRONTE OFICIO</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>CSS 013776/2000</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>CARDINALI ZELMA ANTONIA C/ ANSES S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>11/07/2001</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>16/10/2001: PASE - CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>CSS 023233/2009</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>CARDINALI ZELMA ANTONIA C/ ANSES S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>6/04/2010</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>19/02/2014: PASE - CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>53001224/2010</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 1 - SECRETARIA LEYES ESPECIALES</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>CARDOSO, CARLOS ELBIO BASILIO C/ A.N.S.E.S. - P.E.N. /S AMPARO LEY 16986 Y M</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>EN LETRA</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>27/12/2017</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>27/12/2017: CAMBIO DE ESTADO DE EXPEDIENTE - PARA RETIRAR OFICIO</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>53000601/2011</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 1 - SECRETARIA LEYES ESPECIALES</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>CARIGNANO, BEATRIZ MARIA C/ ANSES S/REAJUSTES POR MOVILIDAD</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>EN LETRA</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>27/12/2017</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>27/12/2017: CAMBIO DE ESTADO DE EXPEDIENTE - PARA RETIRAR OFICIO</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>CSS 009271/2014</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>CARIGNANO BEATRIZ MARIA C/ ANSES S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>8/09/2014</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>8/09/2014: EVENTO - PROV.SIMPLE DEFINITIVA - REMITIDO AL INTERIOR (MGE)</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>CSS 024012/1993</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE LA SEGURIDAD SOCIAL - SALA 1</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>CARLEVARO FEDERICO C/ INPS-CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBL. S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>7/06/2015</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>11/08/1993: PASE - CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBLICOS</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>FRO 031033/2015</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 2 - SECRETARIA LEYES ESPECIALES</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>CARLUTTI, SONIA MARIA C/ ANSES S/EJECUCIÓN PREVISIONAL</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>EN LETRA</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>9/09/2020</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Oficina: LEY: Fecha: 9/09/2020 - Tipo actuacion: MOVIMIENTO</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>53001157/2010</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 1 - SECRETARIA LEYES ESPECIALES</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>CARNIELLO ELBA MARIA C/ A.N.S.E.S. (DR. IDELBERTO BERTOLACCINI) S/VARIOS</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>EN LETRA</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>12/05/2017</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>12/05/2017: CAMBIO DE ESTADO DE EXPEDIENTE - PARA RETIRAR OFICIO</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>53000928/2009</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 1 - SECRETARIA LEYES ESPECIALES</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>CARRASCO BEATRIZ ANTONIA C/ A.N.S.E.S. S/REAJUSTES POR MOVILIDAD</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>EN LETRA</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>17/11/2021</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Oficina: LEY: Fecha: 5/07/2021 - Tipo actuacion: MOVIMIENTO</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>52000161/2012</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 1 - SECRETARIA CIVIL Y COMERCIAL</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>CARRASCO, IGNACIO SALVADOR C/ ANSES S/EJECUCIÓN PREVISIONAL</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>EN LETRA</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>29/03/2022</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Oficina: CIV: Fecha: 29/03/2022 - Tipo actuacion: CEDULA ELECTRONICA PARTE</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>FRO 009658/2025</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE ROSARIO - SALA B</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>CARRASCO, JORGE HUMBERTO C/ ANSES S/REAJUSTE DE HABERES</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>EN LETRA</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Oficina: RSB: Fecha: 24/06/2026 - Tipo actuacion: CEDULA ELECTRONICA PARTE</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>CSS 077985/1994</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE LA SEGURIDAD SOCIAL - SALA 1</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>CARRIO GABRIEL C/ ANSES S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>7/06/2015</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>24/08/1995: PASE - CORTE SUPREMA DE JUSTICIA DE LA NACIÓN</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>CSS 086146/2012</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>CARRION DORA ANITA C/ ANSES S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>26/08/2014</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>11/12/2014: PASE - CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>52000457/2011</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 1 - SECRETARIA CIVIL Y COMERCIAL</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>CARRION, JOSE CARLOS C/ ANSES S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>EN LETRA</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>22/11/2017</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>30/11/2017: CEDULA ELECTRONICA PARTE - CEDULA N° 17000013803814 - NOTIFICADO EL 30/11/2017 15:17</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>FRE 041002498/2012</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE RECONQUISTA - SECRETARIA CIVIL</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>CARRIZO, GLORIA DEL CARMEN C/ ANSES S/PENSIONES</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>EN LETRA</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>18/08/2022</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Oficina: CIV: Fecha: 18/08/2022 - Tipo actuacion: MOVIMIENTO</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>CSS 030965/1991</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE LA SEGURIDAD SOCIAL - SALA 1</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>CASADO ANTONIO C/ INPS-CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBL. S/AMPARO POR MORA DE LA ADMINISTRACION</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>7/06/2015</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>11/12/1991: PASE - CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBLICOS</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>CSS 020780/1992</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE LA SEGURIDAD SOCIAL - SALA 1</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>CASADO ANTONIO C/ INPS-CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBL. S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>7/06/2015</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>12/05/1993: PASE - CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBLICOS</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>CSS 046151/2007</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 2</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>CASALTA CIRINEO ISEO C/ ANSES S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>7/06/2015</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>5/12/2008: PASE - JUZGADO FEDERAL DE SANTA FE 2</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>53001475/2009</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 1 - SECRETARIA LEYES ESPECIALES</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>CASTELLUCCIO, CESAR JUAN C/ A.N.S.E.S. /S ORDINARIO</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>EN LETRA</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>2/08/2018</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>2/08/2018: CAMBIO DE ESTADO DE EXPEDIENTE - PARA RETIRAR OFICIO</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>53000442/2011</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 1 - SECRETARIA LEYES ESPECIALES</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>CASTILLO MARÍA ROSA C/ A.N.S.E.S. S/VARIOS</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>EN LETRA</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>16/06/2017</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>16/06/2017: CAMBIO DE ESTADO DE EXPEDIENTE - PARA RETIRAR OFICIO</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>FRO 015474/2021</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE ROSARIO - SALA B - SECRETARIA CIVIL</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>CASTRO, JOSE ALBERTO C/ ADMINISTRACION NACIONAL DE LA SEGURIDAD SOCIAL (ANSES) S/PENSIONES</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Oficina: CIV: Fecha: 26/06/2026 - Tipo actuacion: MOVIMIENTO</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>CSS 024738/1990</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE LA SEGURIDAD SOCIAL - SALA 1</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>CATTALIN SANTIAGO FEDERICO C/ INPS-COMISION NACIONAL DE PREVISION SOCIAL S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>7/06/2015</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>13/12/1991: PASE - INSTITUTO NACIONAL DE PREVISION SOCIAL</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>FRO 025627/2019</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 1 - SECRETARIA LEYES ESPECIALES</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>CATTANEO, SUSANA MARGARITA JOSEFINA C/ A.N.S.E.S. S/REAJUSTES POR MOVILIDAD</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>EN LETRA</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>13/03/2024</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Oficina: LEY: Fecha: 13/03/2024 - Tipo actuacion: MOVIMIENTO</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>CSS 020937/2014</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>CATUZZI JOSE LUIS C/ ANSES S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>4/09/2014</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>4/09/2014: EVENTO - PROV.SIMPLE DEFINITIVA - REMITIDO AL INTERIOR (MGE)</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>55003180/2011</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 1 - SECRETARIA EJECUCION FISCAL</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>CATUZZI JOSE LUIS C/ ANSES S/VARIOS</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>EN LETRA</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>11/05/2018</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>21/05/2018: CEDULA ELECTRONICA PARTE - CEDULA N° 18000017877592 - NOTIFICADO EL 21/05/2018 14:42</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>CSS 025986/1989</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE LA SEGURIDAD SOCIAL - SALA 2</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>CELERI DE RIVAS ELVA AGUSTINA C/ INPS-CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBL. S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>20/03/1992</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>23/04/1992: PASE - CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBLICOS</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>CSS 006344/1994</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE LA SEGURIDAD SOCIAL - SALA 2</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>CELERI DE RIVAS ELVA AGUSTINA C/ INPS-CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBL. S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>12/04/1994</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>4/08/1994: PASE - CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBLICOS</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>FRO 002388/2014</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE RAFAELA - SECRETARIA CIVIL</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>CELLONE, ATILE DAVID C/ ANSES S/REAJUSTES POR MOVILIDAD</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>EN LETRA</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>15/08/2018</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>15/08/2018: CAMBIO DE ESTADO DE EXPEDIENTE - EN LETRA</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>CSS 025634/1994</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE LA SEGURIDAD SOCIAL - SALA 1</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>CENTURION ELAINES RAMONA C/ INPS-CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBL. S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>7/06/2015</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>24/08/1994: PASE - CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBLICOS</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>CSS 070087/2014</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE LA SEGURIDAD SOCIAL - SALA 3</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>CENTURION SANDRA MONICA C/ ANSES S/RETIRO POR INVALIDEZ (ART 49 P.4. LEY 24,241)</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>GIRO</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>25/03/2021</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Oficina: GS3: Fecha: 25/03/2021 - Tipo actuacion: PASE</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>CSS 032890/1989</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE LA SEGURIDAD SOCIAL - SALA 2</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>CEPEDA JUAN FLORESMIL C/ INPS-CAJA NAC DE PREV DE LA INDUSTRIA,COM Y ACT CIVILES S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>18/10/1990</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>11/02/1991: PASE - CAJA NAC DE PREV DE LA INDUSTRIA, COM Y ACT CIVILES</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>55002426/2011</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 1 - SECRETARIA EJECUCION FISCAL</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>CERDA, MARIA ANA C/ ANSES S/REAJUSTES POR MOVILIDAD</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>EN LETRA</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>8/06/2021</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Oficina: FIS: Fecha: 8/06/2021 - Tipo actuacion: DEO</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>CSS 033976/1992</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE LA SEGURIDAD SOCIAL - SALA 3</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>CERESOLE PEDRO DOMINGO C/ INPS-CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBL. S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>26/11/1993</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>19/04/1995: PASE - CORTE SUPREMA DE JUSTICIA DE LA NACIÓN</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>FRO 025500/2014</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE RAFAELA - SECRETARIA CIVIL</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>CEREZOLE, RENE OMAR C/ ANSES S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>EN LETRA</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>15/08/2018</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>15/08/2018: CAMBIO DE ESTADO DE EXPEDIENTE - EN LETRA</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>CSS 064929/2012</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 2</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>CHAVARINI RICARDO LUIS C/ ANSES S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>10/04/2024</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Oficina: FIS: Fecha: 10/04/2024 - Tipo actuacion: RECEPCION PASE</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>53000213/2011</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 1 - SECRETARIA LEYES ESPECIALES</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>CHAVEZ, MARIA ESTHER C/ A.N.S.E.S. /S ORDINARIO (REAJUSTE</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>EN LETRA</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>8/03/2018</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>8/03/2018: CAMBIO DE ESTADO DE EXPEDIENTE - PARA RETIRAR OFICIO</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>CSS 065432/2013</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>CHAVEZ MARIA ESTHER C/ ANSES S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>7/06/2015</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>13/08/2014: EVENTO - PROV.SIMPLE DEFINITIVA - REMITIDO AL INTERIOR (MGE)</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>53000598/2011</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 1 - SECRETARIA LEYES ESPECIALES</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>CHERVAZ, ANTONIO JOSE C/ ANSES S/REAJUSTES POR MOVILIDAD</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>21/11/2017</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>28/11/2017: CEDULA ELECTRONICA PARTE - CEDULA N° 17000013717914 - NOTIFICADO EL 28/11/2017 10:35</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>CSS 009269/2014</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>CHERVAZ ANTONIO JOSE C/ ANSES S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>19/08/2014</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>19/08/2014: EVENTO - PROV.SIMPLE DEFINITIVA - REMITIDO AL INTERIOR (MGE)</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>FRO 017137/2016</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE RAFAELA - SECRETARIA CIVIL</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>CHIAPERO, HUGO FRANCISCO C/ ANSES S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>EN LETRA</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>31/10/2019</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Oficina: CIV: Fecha: 31/10/2019 - Tipo actuacion: CAMBIO DE ESTADO DE EXPEDIENTE</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>CSS 031754/1993</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE LA SEGURIDAD SOCIAL - SALA 1</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>CHIAPPINI DE BERTOLI VELIA C/ INPS-CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBL. S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>7/06/2015</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>22/09/1993: PASE - CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBLICOS</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>63000426/2011</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 2 - SECRETARIA LEYES ESPECIALES</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>CHIAVARINI RICARDO LUIS C/ ANSES S/EJECUCIÓN PREVISIONAL</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>EN LETRA</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>9/09/2025</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Oficina: LEY: Fecha: 9/09/2025 - Tipo actuacion: MOVIMIENTO</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>CSS 019047/2008</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>CHIOSSO ADELMO FEDERICO C/ ANSES S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>7/06/2015</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>6/11/2008: PASE - CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>CSS 029908/1991</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE LA SEGURIDAD SOCIAL - SALA 1</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>CHIOSSO ADELMO FEDERICO C/ INPS-CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBL. S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>7/06/2015</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>25/10/2005: INFORMACION - COMENTARIO: CERT.SENT.DEF.CUMPLIDA</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>CSS 064519/2007</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>CHUECA FELIPE C/ ANSES S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>7/06/2015</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>27/09/2010: PASE - CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>53000978/2006</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 1 - SECRETARIA LEYES ESPECIALES</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>CHUECA, FELIPE C/ A.N.S.E.S. S/VARIOS</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>19/07/2017</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>19/07/2017: ESCRITO INCORPORADO - solicito orden de pago [Presentado 10/07/2017 15:03] 147 / 148</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>FRO 028532/2014</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE RAFAELA - SECRETARIA CIVIL</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>CIPOLATTI, ELADIO JUAN C/ ANSES S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>SENTENCIA</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>26/02/2026</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Oficina: CIV: Fecha: 26/02/2026 - Tipo actuacion: MOVIMIENTO</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>62000458/2012</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 2 - SECRETARIA CIVIL Y COMERCIAL</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>CIPOLATTI, NORBERTO LUIS C/ ANSES S/EJECUCIÓN PREVISIONAL</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>EN LETRA</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>28/03/2025</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Oficina: CIV: Fecha: 28/03/2025 - Tipo actuacion: MOVIMIENTO</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>52000321/2011</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 1 - SECRETARIA CIVIL Y COMERCIAL</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>CIPOLATTI ROGILDO ALTIVO C/ ANSES S/REAJUSTES POR MOVILIDAD</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>EN LETRA</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>9/05/2018</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>9/05/2018: CAMBIO DE ESTADO DE EXPEDIENTE - EN LETRA</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>CSS 030183/2013</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>CIPOLATTI ROGILDO ALTIVO C/ ANSES S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>28/05/2014</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>28/05/2014: EVENTO - PROV.SIMPLE DEFINITIVA -</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>55001623/2012</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 1 - SECRETARIA EJECUCION FISCAL</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>CLAUSEN OSCAR C/ ANSES S/REAJUSTES POR MOVILIDAD</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>EN LETRA</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>13/07/2019</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>19/03/2018: CAMBIO DE ESTADO DE EXPEDIENTE - EN LETRA</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>CSS 039523/2008</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 2</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>CLOTT BELKYS YOLANDA C/ ANSES S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>22/04/2009</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>18/05/2010: PASE - JUZGADO FEDERAL DE SANTA FE 2</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>CSS 055769/1993</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE LA SEGURIDAD SOCIAL - SALA 3</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>COFINI DELIA MARIA C/ INPS-CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBL. S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>17/06/1994</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>19/10/1994: PASE - ADMINISTRACION NACIONAL DE SEGURIDAD SOCIAL (A.N.Se.S.)</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>FRO 027443/2014</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 1 - SECRETARIA CIVIL Y COMERCIAL</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>COHAN, MARCELO PABLO C/ ANSES S/REAJUSTE DE HABERES</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>EN LETRA</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>27/09/2018</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>27/09/2018: CAMBIO DE ESTADO DE EXPEDIENTE - PARA RETIRAR OFICIO</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>CSS 014574/1992</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE LA SEGURIDAD SOCIAL - SALA 2</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>COLAUTTI DE GOMEZ GLADYS C/ INPS-CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBL. S/AMPARO POR MORA DE LA ADMINISTRACION</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>18/11/1992</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>9/12/1993: PASE - CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBLICOS</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>CSS 017732/1994</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE LA SEGURIDAD SOCIAL - SALA 2</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>COLAUTTI DE GOMEZ GLADYS C/ INPS-CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBL. S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>24/08/1994</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>20/03/1998: INFORMACION - COMENTARIO: OF. A LA C.S.J.N.</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>53000792/2010</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 1 - SECRETARIA LEYES ESPECIALES</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>COLMAN, LUIS ALBERTO C/ A.N.S.E.S. /S ORDINARIO</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>EN LETRA</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>11/04/2016</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>11/04/2016: FIRMA DESPACHO - AGREGUESE OFICIO DE REMISIÓN DE ADM Y COPIAS CERTIFICADAS 92 / 92</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>CSS 059079/2013</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 2</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>COLODRERO ELIO OMAR C/ ANSES S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>15/08/2014</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>15/08/2014: EVENTO - PROV.SIMPLE DEFINITIVA - REMITIDO AL INTERIOR (MGE)</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>CSS 012653/1992</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE LA SEGURIDAD SOCIAL - SALA 1</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>CONSUEGRA BETHY MARIA C/ INPS-CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBL. S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>7/06/2015</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>12/05/1993: PASE - CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBLICOS</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>CSS 013696/2008</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>CORDERO GERMINAL C/ ANSES S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>7/06/2015</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>5/12/2008: PASE - CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>CSS 030692/1991</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE LA SEGURIDAD SOCIAL - SALA 1</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>CORDERO GERMINAL C/ INPS-CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBL. S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>7/06/2015</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>10/02/2006: INFORMACION - COMENTARIO: PRIMERA CERT.SENT.DEF.CUMPLIDA</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>CSS 012689/1992</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE LA SEGURIDAD SOCIAL - SALA 3</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>CORDOBA DE BORDON MARIA C/ INPS-CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBL. S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>28/04/1993</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>18/06/1993: PASE - CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBLICOS</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>FRO 042840/2018</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE ROSARIO - SALA B</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>CORDOBA, FELIX SANTIAGO C/ ANSES S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>GIRO</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Oficina: MEC: Fecha: 30/06/2026 - Tipo actuacion: PASE</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>CSS 015105/1992</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE LA SEGURIDAD SOCIAL - SALA 2</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>CORDOBA HILMA C/ INPS-CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBL. S/AMPARO POR MORA DE LA ADMINISTRACION</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>EN LETRA</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>19/12/1994</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>15/12/2000: INFORMACION - NOTIF. A LA PROCURACION</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>CSS 065713/1993</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE LA SEGURIDAD SOCIAL - SALA 2</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>CORDOBA HILMA RUBEN C/ INPS-CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBL. S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>7/06/2015</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>16/03/2004: INFORMACION - COMENTARIO: SE REM A ANSES P/SER AGREG AL PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>63000395/2011</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 2 - SECRETARIA LEYES ESPECIALES</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>CORDOBA, LUCIA CRISTINA C/ ANSES S/EJECUCIÓN PREVISIONAL</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>EN LETRA</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>4/03/2026</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Oficina: LEY: Fecha: 4/03/2026 - Tipo actuacion: MOVIMIENTO</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>CSS 066968/2013</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 2</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>CORDOBA LUCIA CRISTINA C/ ANSES S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>13/08/2014</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>13/08/2014: EVENTO - PROV.SIMPLE DEFINITIVA - REMITIDO AL INTERIOR (MGE)</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>FRO 015134/2013</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 1 - SECRETARIA EJECUCION FISCAL</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>CORDOBA, MIGUEL SANTOS C/ ANSES S/EJECUCION DE SENTENCIA</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>EN LETRA</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>8/08/2022</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Oficina: FIS: Fecha: 8/08/2022 - Tipo actuacion: DEO</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>55002592/2011</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 1 - SECRETARIA EJECUCION FISCAL</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>CORDOBA NIDIA BEATRIZ C/ ANSES S/VARIOS</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>EN LETRA</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>18/12/2025</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Oficina: FIS: Fecha: 18/12/2025 - Tipo actuacion: DEO</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>CSS 013812/2000</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>CORTOPASSI ALBERTO C/ ANSES S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>1/10/2001</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>7/12/2001: PASE - CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>CSS 029762/1990</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE LA SEGURIDAD SOCIAL - SALA 1</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>COSTAMAGNA DE SABATINI INES C/ INPS-COMISION NACIONAL DE PREVISION SOCIAL S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>7/06/2015</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>24/10/2005: INFORMACION - COMENTARIO: CERT.SENT.DEF.CUMPLIDA</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>53000544/2007</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 1 - SECRETARIA LEYES ESPECIALES</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>COSTAMAGNA, INES MARIA C/ ANSES S/EJECUCION DE SENTENCIA</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>EN LETRA</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>12/02/2026</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Oficina: LEY: Fecha: 12/02/2026 - Tipo actuacion: DEO</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>CSS 072004/2009</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>COSTAMAGNA INES MARIA C/ ANSES S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>12/08/2010</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>28/09/2010: PASE - CAMARA FEDERAL DE ROSARIO - MESA DE ENTRADAS SANTA FE - 1RA INSTANCIA</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>FRO 040266/2019</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE ROSARIO - SALA A - SECRETARIA CIVIL</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>CRAVERO, AVELINO RAUL C/ ANSES S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>SENTENCIA</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Oficina: CIV: Fecha: 29/04/2026 - Tipo actuacion: MOVIMIENTO</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>CSS 024515/1990</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE LA SEGURIDAD SOCIAL - SALA 1</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>CRESPI OSCAR HECTOR C/ INPS-CAJA NAC DE PREV PARA EL PERS DEL EST Y SERV PUBL. S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>7/06/2015</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>25/10/2005: INFORMACION - COMENTARIO: CERT.SENT.DEF.CUMPLIDA</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>CSS 085579/2009</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 2</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>CRESPO HUMBERTO ALVARO C/ ANSES S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>16/12/2010</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>19/09/2011: PASE - JUZGADO FEDERAL DE SANTA FE 2</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>55003173/2011</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 1 - SECRETARIA EJECUCION FISCAL</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>CUARANTA AMERICO ARGENTINO C/ ANSES S/REAJUSTES POR MOVILIDAD</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>EN LETRA</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>3/03/2017</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>3/03/2017: CAMBIO DE ESTADO DE EXPEDIENTE - EN LETRA</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>53001853/2009</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 1 - SECRETARIA LEYES ESPECIALES</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>CULASSO, ROGELIO PEDRO RICARDO C/ A.N.S.E.S. S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>EN LETRA</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>22/10/2018</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>22/10/2018: CEDULA ELECTRONICA TRIBUNAL - CEDULA N° 18000021588210 - NOTIFICADO EL DIA: 22/10/2018 11:44</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>CSS 020727/2013</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SALTA 1</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>CULASSO ROGELIO PEDRO RICARDO C/ ANSES S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>29/05/2014</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>29/05/2014: EVENTO - PROV.SIMPLE DEFINITIVA -</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>CSS 017662/2014</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>JUZGADO FEDERAL DE SANTA FE 2</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>CULLERES NORMA BELKYS C/ ANSES S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>15/08/2014</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>15/08/2014: EVENTO - PROV.SIMPLE DEFINITIVA - REMITIDO AL INTERIOR (MGE)</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>CSS 029574/1990</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE LA SEGURIDAD SOCIAL - SALA 2</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>CURTI DE MELLADO GEMA LINA C/ INPS-COMISION NACIONAL DE PREVISION SOCIAL S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>23/04/1992</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>CSS 029574/1990</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>CAMARA FEDERAL DE LA SEGURIDAD SOCIAL - SALA 2</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>CURTI DE MELLADO GEMA LINA C/ INPS-COMISION NACIONAL DE PREVISION SOCIAL S/REAJUSTES VARIOS</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>EN DESPACHO</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>23/04/1992</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>No pude volver a la lista</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/expedientes_pjn_detalle.xlsx
+++ b/expedientes_pjn_detalle.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,37 +429,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Número de expediente</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Juzgado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Carátula</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Situación</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Últ. Act. listado</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Último movimiento</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Error</t>
         </is>
@@ -25988,7 +26000,11 @@
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="F775" t="inlineStr"/>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>30/06/2026: CEDULA ELECTRONICA TRIBUNAL - CEDULA N° 26000109152788 - NOTIFICADO EL DIA: 30/06/2026 12:55</t>
+        </is>
+      </c>
       <c r="G775" t="inlineStr"/>
     </row>
     <row r="776">
@@ -26149,24 +26165,12 @@
           <t>5/04/1994</t>
         </is>
       </c>
-      <c r="F780" t="inlineStr"/>
-      <c r="G780" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Locator.click: Timeout 30000ms exceeded.
-Call log:
-  - waiting for get_by_text("Ver históricas")
-    - locator resolved to &lt;span&gt;…&lt;/span&gt;
-  - attempting click action
-    - waiting for element to be visible, enabled and stable
-    - element is visible, enabled and stable
-    - scrolling into view if needed
-    - done scrolling
-    - performing click action
-    - click action done
-    - waiting for scheduled navigations to finish
-</t>
-        </is>
-      </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>3/06/1994: PASE - CORTE SUPREMA DE JUSTICIA DE LA NACIÓN</t>
+        </is>
+      </c>
+      <c r="G780" t="inlineStr"/>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
@@ -26194,7 +26198,11 @@
           <t>5/04/2024</t>
         </is>
       </c>
-      <c r="F781" t="inlineStr"/>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>5/04/2024: MOVIMIENTO - EN LETRA</t>
+        </is>
+      </c>
       <c r="G781" t="inlineStr"/>
     </row>
     <row r="782">
@@ -26355,7 +26363,11 @@
           <t>29/03/2019</t>
         </is>
       </c>
-      <c r="F786" t="inlineStr"/>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>29/03/2019: CAMBIO DE ESTADO DE EXPEDIENTE - EN LETRA</t>
+        </is>
+      </c>
       <c r="G786" t="inlineStr"/>
     </row>
     <row r="787">
@@ -26450,7 +26462,11 @@
           <t>2/03/2018</t>
         </is>
       </c>
-      <c r="F789" t="inlineStr"/>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>28/02/2018: FIRMA DESPACHO - ANSES- CERTIFICACION FOTOCOPIAS SIN ADMINISTRATIVOS Y OFICIO + CERTIFICACION FINAL 140 / 141</t>
+        </is>
+      </c>
       <c r="G789" t="inlineStr"/>
     </row>
     <row r="790">
@@ -26677,7 +26693,11 @@
           <t>12/10/2023</t>
         </is>
       </c>
-      <c r="F796" t="inlineStr"/>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>12/10/2023: MOVIMIENTO - EN LETRA</t>
+        </is>
+      </c>
       <c r="G796" t="inlineStr"/>
     </row>
     <row r="797">
@@ -27267,7 +27287,11 @@
           <t>21/12/2022</t>
         </is>
       </c>
-      <c r="F814" t="inlineStr"/>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>21/12/2022: MOVIMIENTO - EN LETRA</t>
+        </is>
+      </c>
       <c r="G814" t="inlineStr"/>
     </row>
     <row r="815">
@@ -27362,7 +27386,11 @@
           <t>9/02/2026</t>
         </is>
       </c>
-      <c r="F817" t="inlineStr"/>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>9/02/2026: MOVIMIENTO - ESPERANDO EXPRESION DE AGRAVIOS</t>
+        </is>
+      </c>
       <c r="G817" t="inlineStr"/>
     </row>
     <row r="818">
@@ -27457,7 +27485,11 @@
           <t>24/09/2019</t>
         </is>
       </c>
-      <c r="F820" t="inlineStr"/>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>24/09/2019: CAMBIO DE ESTADO DE EXPEDIENTE - EN LETRA</t>
+        </is>
+      </c>
       <c r="G820" t="inlineStr"/>
     </row>
     <row r="821">
@@ -27948,7 +27980,11 @@
           <t>26/02/2026</t>
         </is>
       </c>
-      <c r="F835" t="inlineStr"/>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>26/02/2026: MOVIMIENTO - EN LETRA</t>
+        </is>
+      </c>
       <c r="G835" t="inlineStr"/>
     </row>
     <row r="836">
@@ -28010,7 +28046,11 @@
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="F837" t="inlineStr"/>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>27/05/2026: CEDULA ELECTRONICA PARTE - CEDULA N° 26000107607991 - NOTIFICADO EL 27/05/2026 10:57</t>
+        </is>
+      </c>
       <c r="G837" t="inlineStr"/>
     </row>
     <row r="838">
@@ -28072,7 +28112,11 @@
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="F839" t="inlineStr"/>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>26/05/2026: MOVIMIENTO - EN LETRA</t>
+        </is>
+      </c>
       <c r="G839" t="inlineStr"/>
     </row>
     <row r="840">
@@ -28101,7 +28145,11 @@
           <t>26/06/2026</t>
         </is>
       </c>
-      <c r="F840" t="inlineStr"/>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>26/06/2026: FIRMA DESPACHO - SE RECTIFICA DECRETO 181 / 181</t>
+        </is>
+      </c>
       <c r="G840" t="inlineStr"/>
     </row>
     <row r="841">
@@ -28163,7 +28211,11 @@
           <t>23/12/2020</t>
         </is>
       </c>
-      <c r="F842" t="inlineStr"/>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>23/12/2020: ESCRITO INCORPORADO - INFORMA IMPOSIBILIDAD CUMPLIMIENTO [Presentado 10/02/2020 12:18] 98 / 98</t>
+        </is>
+      </c>
       <c r="G842" t="inlineStr"/>
     </row>
     <row r="843">
@@ -28324,7 +28376,11 @@
           <t>5/04/2018</t>
         </is>
       </c>
-      <c r="F847" t="inlineStr"/>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>28/02/2018: FIRMA DESPACHO - DECRETO ORDENANDO LA CERTIFICACIÓN DE LAS FOTOCOPIAS ACOMPAÑADAS Y EL RETIRO DEL EXPEDIENTE ADMINISTRATIVO 69 / 69</t>
+        </is>
+      </c>
       <c r="G847" t="inlineStr"/>
     </row>
     <row r="848">
@@ -28353,7 +28409,11 @@
           <t>30/08/2024</t>
         </is>
       </c>
-      <c r="F848" t="inlineStr"/>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>30/08/2024: MOVIMIENTO - SENTENCIAS INTERLOC PARA REGUL</t>
+        </is>
+      </c>
       <c r="G848" t="inlineStr"/>
     </row>
     <row r="849">
@@ -28415,7 +28475,11 @@
           <t>27/11/2023</t>
         </is>
       </c>
-      <c r="F850" t="inlineStr"/>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>27/11/2023: MOVIMIENTO - EN LETRA</t>
+        </is>
+      </c>
       <c r="G850" t="inlineStr"/>
     </row>
     <row r="851">
@@ -28543,7 +28607,11 @@
           <t>2/07/2024</t>
         </is>
       </c>
-      <c r="F854" t="inlineStr"/>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>2/07/2024: DEO - SE RECIBIO DEO: 14545700 - OFICIO COMUNICACIÓN - 60000015379 - BANCO NACION - SANTA FE - SANTA FE (3330)</t>
+        </is>
+      </c>
       <c r="G854" t="inlineStr"/>
     </row>
     <row r="855">
@@ -28638,7 +28706,11 @@
           <t>14/06/2021</t>
         </is>
       </c>
-      <c r="F857" t="inlineStr"/>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>14/06/2021: MOVIMIENTO - EN LETRA</t>
+        </is>
+      </c>
       <c r="G857" t="inlineStr"/>
     </row>
     <row r="858">
@@ -28799,7 +28871,11 @@
           <t>4/02/2020</t>
         </is>
       </c>
-      <c r="F862" t="inlineStr"/>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>4/02/2020: CAMBIO DE ESTADO DE EXPEDIENTE - EN LETRA</t>
+        </is>
+      </c>
       <c r="G862" t="inlineStr"/>
     </row>
     <row r="863">
@@ -28828,7 +28904,11 @@
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="F863" t="inlineStr"/>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>27/05/2026: FIRMA DESPACHO - PLAN DE ACCION + LIQUIDACION ADM 323 / 323</t>
+        </is>
+      </c>
       <c r="G863" t="inlineStr"/>
     </row>
     <row r="864">
@@ -29055,7 +29135,11 @@
           <t>28/04/2022</t>
         </is>
       </c>
-      <c r="F870" t="inlineStr"/>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>28/04/2022: CAMBIO DE ESTADO DE EXPEDIENTE - SIN DEFINIR</t>
+        </is>
+      </c>
       <c r="G870" t="inlineStr"/>
     </row>
     <row r="871">
@@ -29117,7 +29201,11 @@
           <t>28/09/2023</t>
         </is>
       </c>
-      <c r="F872" t="inlineStr"/>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>28/09/2023: MOVIMIENTO - EN LETRA</t>
+        </is>
+      </c>
       <c r="G872" t="inlineStr"/>
     </row>
     <row r="873">
@@ -29311,7 +29399,11 @@
           <t>1/06/2026</t>
         </is>
       </c>
-      <c r="F878" t="inlineStr"/>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>1/06/2026: MOVIMIENTO - EN LETRA</t>
+        </is>
+      </c>
       <c r="G878" t="inlineStr"/>
     </row>
     <row r="879">
@@ -29373,7 +29465,11 @@
           <t>20/11/2014</t>
         </is>
       </c>
-      <c r="F880" t="inlineStr"/>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>20/11/2014: MOVIMIENTO - EN LETRA</t>
+        </is>
+      </c>
       <c r="G880" t="inlineStr"/>
     </row>
     <row r="881">
@@ -29402,12 +29498,12 @@
           <t>20/11/2014</t>
         </is>
       </c>
-      <c r="F881" t="inlineStr"/>
-      <c r="G881" t="inlineStr">
-        <is>
-          <t>No pude volver a la lista</t>
-        </is>
-      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>20/11/2014: MOVIMIENTO - EN LETRA</t>
+        </is>
+      </c>
+      <c r="G881" t="inlineStr"/>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
@@ -29567,7 +29663,11 @@
           <t>26/12/2023</t>
         </is>
       </c>
-      <c r="F886" t="inlineStr"/>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>26/12/2023: MOVIMIENTO - EN LETRA</t>
+        </is>
+      </c>
       <c r="G886" t="inlineStr"/>
     </row>
     <row r="887">
@@ -29662,7 +29762,11 @@
           <t>2/09/2025</t>
         </is>
       </c>
-      <c r="F889" t="inlineStr"/>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>2/09/2025: DEO - SE RECIBIO DEO: 19854257 - OFICIO COMUNICACIÓN - 60000015379 - BANCO NACION - SANTA FE - SANTA FE (3330)</t>
+        </is>
+      </c>
       <c r="G889" t="inlineStr"/>
     </row>
     <row r="890">
@@ -29823,7 +29927,11 @@
           <t>24/08/2022</t>
         </is>
       </c>
-      <c r="F894" t="inlineStr"/>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>24/08/2022: FIRMA DESPACHO - A LO SOLICITADO, ACLARE 165 / 165</t>
+        </is>
+      </c>
       <c r="G894" t="inlineStr"/>
     </row>
     <row r="895">
@@ -29885,7 +29993,11 @@
           <t>13/08/2025</t>
         </is>
       </c>
-      <c r="F896" t="inlineStr"/>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>13/08/2025: MOVIMIENTO - EN LETRA</t>
+        </is>
+      </c>
       <c r="G896" t="inlineStr"/>
     </row>
     <row r="897">
@@ -29980,7 +30092,11 @@
           <t>4/06/2026</t>
         </is>
       </c>
-      <c r="F899" t="inlineStr"/>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>4/06/2026: DEO - ENVIO DEO A ENTIDAD EXTERNA: 23391855 - OFICIO COMUNICACIÓN - 60000015379 - BANCO NACION - SANTA FE - SANTA FE (3330)</t>
+        </is>
+      </c>
       <c r="G899" t="inlineStr"/>
     </row>
     <row r="900">
@@ -30108,7 +30224,11 @@
           <t>28/04/2021</t>
         </is>
       </c>
-      <c r="F903" t="inlineStr"/>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>29/11/2021: CEDULA ELECTRONICA PARTE - CEDULA N° 21000049867495 - NOTIFICADO EL 29/11/2021 18:44</t>
+        </is>
+      </c>
       <c r="G903" t="inlineStr"/>
     </row>
     <row r="904">
@@ -30203,7 +30323,11 @@
           <t>19/05/2014</t>
         </is>
       </c>
-      <c r="F906" t="inlineStr"/>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>19/05/2014: EVENTO - PROV.SIMPLE DEFINITIVA -</t>
+        </is>
+      </c>
       <c r="G906" t="inlineStr"/>
     </row>
     <row r="907">
@@ -30232,12 +30356,12 @@
           <t>19/05/2014</t>
         </is>
       </c>
-      <c r="F907" t="inlineStr"/>
-      <c r="G907" t="inlineStr">
-        <is>
-          <t>No pude volver a la lista</t>
-        </is>
-      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>19/05/2014: EVENTO - PROV.SIMPLE DEFINITIVA -</t>
+        </is>
+      </c>
+      <c r="G907" t="inlineStr"/>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
@@ -30430,7 +30554,11 @@
           <t>29/04/2019</t>
         </is>
       </c>
-      <c r="F913" t="inlineStr"/>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>29/04/2019: CAMBIO DE ESTADO DE EXPEDIENTE - EN LETRA</t>
+        </is>
+      </c>
       <c r="G913" t="inlineStr"/>
     </row>
     <row r="914">
@@ -30525,7 +30653,11 @@
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="F916" t="inlineStr"/>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>10/06/2026: MOVIMIENTO - EN LETRA</t>
+        </is>
+      </c>
       <c r="G916" t="inlineStr"/>
     </row>
     <row r="917">
@@ -30620,7 +30752,11 @@
           <t>5/06/2019</t>
         </is>
       </c>
-      <c r="F919" t="inlineStr"/>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>10/05/2019: CAMBIO DE ESTADO DE EXPEDIENTE - SENTENCIA DEFINITIVA</t>
+        </is>
+      </c>
       <c r="G919" t="inlineStr"/>
     </row>
     <row r="920">
@@ -30748,7 +30884,11 @@
           <t>26/06/2026</t>
         </is>
       </c>
-      <c r="F923" t="inlineStr"/>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>26/06/2026: DEO - ENVIO DEO A ENTIDAD EXTERNA: 23707109 - OFICIO COMUNICACIÓN - 60000015379 - BANCO NACION - SANTA FE - SANTA FE (3330)</t>
+        </is>
+      </c>
       <c r="G923" t="inlineStr"/>
     </row>
     <row r="924">
@@ -30909,7 +31049,11 @@
           <t>18/06/2025</t>
         </is>
       </c>
-      <c r="F928" t="inlineStr"/>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>18/06/2025: MOVIMIENTO - PARA SENTENCIA PREVIO SORTEO</t>
+        </is>
+      </c>
       <c r="G928" t="inlineStr"/>
     </row>
     <row r="929">
@@ -31136,7 +31280,11 @@
           <t>2/06/2023</t>
         </is>
       </c>
-      <c r="F935" t="inlineStr"/>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>2/06/2023: MOVIMIENTO - EN LETRA</t>
+        </is>
+      </c>
       <c r="G935" t="inlineStr"/>
     </row>
     <row r="936">
@@ -31198,7 +31346,11 @@
           <t>5/11/2024</t>
         </is>
       </c>
-      <c r="F937" t="inlineStr"/>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>5/11/2024: MOVIMIENTO - EN LETRA</t>
+        </is>
+      </c>
       <c r="G937" t="inlineStr"/>
     </row>
     <row r="938">
@@ -31227,7 +31379,11 @@
           <t>24/10/2025</t>
         </is>
       </c>
-      <c r="F938" t="inlineStr"/>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>24/10/2025: DEO - SE RECIBIO DEO: 20631341 - OFICIO COMUNICACIÓN - 60000015379 - BANCO NACION - SANTA FE - SANTA FE (3330)</t>
+        </is>
+      </c>
       <c r="G938" t="inlineStr"/>
     </row>
     <row r="939">
@@ -31289,7 +31445,11 @@
           <t>11/09/2020</t>
         </is>
       </c>
-      <c r="F940" t="inlineStr"/>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>23/09/2020: CEDULA ELECTRONICA PARTE - CEDULA N° 20000037883495 - NOTIFICADO EL 23/09/2020 16:45</t>
+        </is>
+      </c>
       <c r="G940" t="inlineStr"/>
     </row>
     <row r="941">
@@ -31384,7 +31544,11 @@
           <t>20/03/2024</t>
         </is>
       </c>
-      <c r="F943" t="inlineStr"/>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>20/03/2024: MOVIMIENTO - EN LETRA</t>
+        </is>
+      </c>
       <c r="G943" t="inlineStr"/>
     </row>
     <row r="944">
